--- a/EventLogs_May20-2025/log_analysis.xlsx
+++ b/EventLogs_May20-2025/log_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="183">
   <si>
     <t>id</t>
   </si>
@@ -32,679 +32,529 @@
     <t>step duration</t>
   </si>
   <si>
+    <t>logs downloaded</t>
+  </si>
+  <si>
     <t>multiple download - acknowledge</t>
   </si>
   <si>
-    <t>multiple download - parseLogs</t>
-  </si>
-  <si>
-    <t>multiple download - saveLogs</t>
-  </si>
-  <si>
-    <t>saveSLogs</t>
-  </si>
-  <si>
-    <t>saveTLogs</t>
-  </si>
-  <si>
-    <t>saveAvgTLogs</t>
-  </si>
-  <si>
-    <t>insertJobNumberToTLogs</t>
-  </si>
-  <si>
-    <t>insertJobNumberToAvgTLogs</t>
-  </si>
-  <si>
-    <t>saveTiltViewLogs</t>
-  </si>
-  <si>
-    <t>log-service</t>
+    <t>multiple download - saveLogs Completed</t>
   </si>
   <si>
     <t>Total processing time</t>
   </si>
   <si>
-    <t>multiple download - saveLogs Completed</t>
+    <t>Total logs downloaded</t>
   </si>
   <si>
     <t>INFO : 15:32:32:648  - log-service  - socket onopen  - &gt;&gt;&gt; e.data: 132000</t>
   </si>
   <si>
-    <t>INFO : 15:32:46:915  - logsToDbHelper  - parseLogs  - START</t>
-  </si>
-  <si>
-    <t>INFO : 15:32:48:636  - log-service  - saveAllLogs  - START</t>
-  </si>
-  <si>
-    <t>INFO : 15:32:50:524  - log-service  - saveSLogs  - END-counter</t>
-  </si>
-  <si>
-    <t>INFO : 15:32:59:124  - log-service  - saveTLogs  - END-counter</t>
-  </si>
-  <si>
-    <t>INFO : 15:34:10:427  - log-service  - saveAvgTLogs  - END-counter</t>
-  </si>
-  <si>
-    <t>INFO : 15:34:10:437  - log-service  - insertJobNumberToTLogs  - START</t>
-  </si>
-  <si>
-    <t>INFO : 15:34:10:438  - log-service  - insertJobNumberToAvgTLogs  - START</t>
-  </si>
-  <si>
-    <t>INFO : 15:34:11:842  - log-service  - saveTiltViewLogs  - END-counter</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:18:809  - log-service  - JOB NUMBER to TLogs  -</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:29:632  - log-service  - JOB NUMBER to AvgTlogs  -</t>
-  </si>
-  <si>
     <t>INFO : 15:35:29:670  - projectMaster-service  - welding_system  -   [{"welding_system":"{\"P600Z\":true,\"P625\":true,\"M500\":true}"}]</t>
   </si>
   <si>
     <t>INFO : 15:45:10:939  - log-service  - socket onopen  - &gt;&gt;&gt; e.data: 132000</t>
   </si>
   <si>
-    <t>INFO : 15:46:01:873  - logsToDbHelper  - parseLogs  - START</t>
-  </si>
-  <si>
-    <t>INFO : 15:46:03:376  - log-service  - saveAllLogs  - START</t>
-  </si>
-  <si>
-    <t>INFO : 15:46:05:154  - log-service  - saveSLogs  - END-counter</t>
-  </si>
-  <si>
-    <t>INFO : 15:46:12:726  - log-service  - saveTLogs  - END-counter</t>
-  </si>
-  <si>
-    <t>INFO : 15:47:20:166  - log-service  - saveAvgTLogs  - END-counter</t>
-  </si>
-  <si>
-    <t>INFO : 15:47:20:175  - log-service  - insertJobNumberToTLogs  - START</t>
-  </si>
-  <si>
-    <t>INFO : 15:47:20:176  - log-service  - insertJobNumberToAvgTLogs  - START</t>
-  </si>
-  <si>
-    <t>INFO : 15:47:21:501  - log-service  - saveTiltViewLogs  - END-counter</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:03:213  - log-service  - JOB NUMBER to TLogs  -</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:49:089  - log-service  - JOB NUMBER to AvgTlogs  -</t>
-  </si>
-  <si>
     <t>INFO : 15:52:49:122  - projectMaster-service  - welding_system  -   [{"welding_system":"{\"P600Z\":true,\"P625\":true,\"M500\":true}"}]</t>
   </si>
   <si>
     <t>3:32:32 PM</t>
   </si>
   <si>
-    <t>3:32:46 PM</t>
-  </si>
-  <si>
-    <t>3:32:48 PM</t>
-  </si>
-  <si>
-    <t>3:32:50 PM</t>
-  </si>
-  <si>
-    <t>3:32:59 PM</t>
-  </si>
-  <si>
-    <t>3:34:10 PM</t>
-  </si>
-  <si>
-    <t>3:34:11 PM</t>
-  </si>
-  <si>
-    <t>3:35:18 PM</t>
+    <t>3:35:29 PM</t>
   </si>
   <si>
     <t>0:02:57</t>
   </si>
   <si>
-    <t>3:35:29 PM</t>
-  </si>
-  <si>
     <t>3:45:10 PM</t>
   </si>
   <si>
-    <t>3:46:01 PM</t>
-  </si>
-  <si>
-    <t>3:46:03 PM</t>
-  </si>
-  <si>
-    <t>3:46:05 PM</t>
-  </si>
-  <si>
-    <t>3:46:12 PM</t>
-  </si>
-  <si>
-    <t>3:47:20 PM</t>
-  </si>
-  <si>
-    <t>3:47:21 PM</t>
-  </si>
-  <si>
-    <t>3:52:03 PM</t>
+    <t>3:52:49 PM</t>
   </si>
   <si>
     <t>0:07:39</t>
   </si>
   <si>
-    <t>3:52:49 PM</t>
-  </si>
-  <si>
-    <t>0:00:14</t>
+    <t>Status calculation start</t>
+  </si>
+  <si>
+    <t>total tlogs in project</t>
+  </si>
+  <si>
+    <t>Total status calculation time</t>
+  </si>
+  <si>
+    <t>setIncomplete flag</t>
+  </si>
+  <si>
+    <t>status update</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:30:145  - CalculatingStatusModal  - startCalculating  - Start</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:31:995  - log-service  - checkTLogsExistenceByProjectId  - Rowcount: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:32:583  - log-service  - setIncompleteFlagTRecords  - Updated in s_logs, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:32:583  - log-service  - setIncompleteFlagTRecords  - Updated, Rows affected : 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:32:242  - CalculatingStatusModal  - startCalculating  - End</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:32:234  - CalculatingStatusModal  - startCalculating  - dbHelper-start</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:32:583  - log-service  - setIncompleteFlagTRecords  - Updated in clear, Rows affected: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:32:225  - CalculatingStatusModal  - startCalculating  - WeldParameters: true</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:32:211  - CalculatingStatusModal  - startCalculating  - tLogsPresent: true</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:34:101  - log-service  - updateLeadGroupNameTrailGroupName  - Updated, Rows affected : 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:34:577  - log-service  - updateColumnStatus called from: Lead Calculation - Starting  - Updated, Rows affected: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:35:062  - log-service  - updateColumnStatus called from: Lead Calculation - Lead STATUS  - Updated, Rows affected: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:38:380  - log-service  - updateColumnStatus called from: leadStatus - volts  - Updated, Rows affected: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:41:579  - log-service  - updateColumnStatus called from: leadStatus - current  - Updated, Rows affected: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:44:804  - log-service  - updateColumnStatus called from: leadStatus - wire speed  - Updated, Rows affected: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:48:078  - log-service  - updateColumnStatus called from: leadStatus - travel speed  - Updated, Rows affected: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:51:393  - log-service  - updateColumnStatus called from: leadStatus - oscillation width  - Updated, Rows affected: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:51:698  - log-service  - updateColumnStatus called from: Lead Calculation - Completing  - Updated, Rows affected: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:52:156  - log-service  - updateColumnStatus called from: trail Calculation - Starting  - Updated, Rows affected: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:52:614  - log-service  - updateColumnStatus called from: trail Calculation - Trail STATUS  - Updated, Rows affected: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:53:741  - log-service  - updateColumnStatus called from: trailStatus - volts  - Updated, Rows affected: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:54:614  - log-service  - updateColumnStatus called from: trailStatus - current  - Updated, Rows affected: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:55:693  - log-service  - updateColumnStatus called from: trailStatus - travel speed  - Updated, Rows affected: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:55:335  - log-service  - updateColumnStatus called from: trailStatus - wire speed  - Updated, Rows affected: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:56:078  - log-service  - updateColumnStatus called from: trailStatus - oscillation width  - Updated, Rows affected: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:56:371  - log-service  - updateColumnStatus called from: Trail Calculation - Completing  - Updated, Rows affected: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:35:56:564  - log-service  - statusCrossCheck  - Updated, Rows affected : 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:36:00:927  - log-service  - trueAvgStatus  - Updated, Rows affected: 20000</t>
+  </si>
+  <si>
+    <t>INFO : 15:39:18:233  - log-service  - trueTiltStatus  - Updated, Rows affected: 16000</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:11:045  - log-service  - updateColumnStatus called from: updateSLogsStatusFromTLogsStatus-Demo  - Updated, Rows affected: 4000</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:11:466  - log-service  - updateColumnStatus called from: Lead Calculation - Starting  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:11:598  - log-service  - updateColumnStatus called from: Lead Calculation - Lead STATUS  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:11:735  - log-service  - updateColumnStatus called from: leadStatus - volts  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:11:813  - log-service  - updateColumnStatus called from: leadStatus - current  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:11:918  - log-service  - updateColumnStatus called from: leadStatus - wire speed  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:12:701  - log-service  - updateColumnStatus called from: trail Calculation - Trail STATUS  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:12:992  - log-service  - updateColumnStatus called from: trailStatus - wire speed  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:12:892  - log-service  - updateColumnStatus called from: trailStatus - current  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:12:792  - log-service  - updateColumnStatus called from: trailStatus - volts  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:12:261  - log-service  - updateColumnStatus called from: Lead Calculation - Completing  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:12:145  - log-service  - updateColumnStatus called from: leadStatus - oscillation width  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:12:028  - log-service  - updateColumnStatus called from: leadStatus - travel speed  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:12:628  - log-service  - updateColumnStatus called from: trail Calculation - Starting  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:13:092  - log-service  - updateColumnStatus called from: trailStatus - travel speed  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:13:192  - log-service  - updateColumnStatus called from: trailStatus - oscillation width  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:13:309  - log-service  - updateColumnStatus called from: Trail Calculation - Completing  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:13:623  - log-service  - statusCrossCheck  - Updated, Rows affected : 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:14:809  - log-service  - updateColumnStatus called from: leadStatus - current  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:14:008  - log-service  - updateColumnStatus called from: updateSLogsStatusFromTLogsStatus-Demo_1  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:14:468  - log-service  - updateColumnStatus called from: Lead Calculation - Starting  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:14:575  - log-service  - updateColumnStatus called from: Lead Calculation - Lead STATUS  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:14:692  - log-service  - updateColumnStatus called from: leadStatus - volts  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:14:908  - log-service  - updateColumnStatus called from: leadStatus - wire speed  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:15:841  - log-service  - updateColumnStatus called from: trailStatus - current  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:15:941  - log-service  - updateColumnStatus called from: trailStatus - wire speed  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:15:631  - log-service  - updateColumnStatus called from: trail Calculation - Trail STATUS  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:15:742  - log-service  - updateColumnStatus called from: trailStatus - volts  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:15:207  - log-service  - updateColumnStatus called from: Lead Calculation - Completing  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:15:557  - log-service  - updateColumnStatus called from: trail Calculation - Starting  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:15:107  - log-service  - updateColumnStatus called from: leadStatus - oscillation width  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:15:008  - log-service  - updateColumnStatus called from: leadStatus - travel speed  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:16:041  - log-service  - updateColumnStatus called from: trailStatus - travel speed  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:16:140  - log-service  - updateColumnStatus called from: trailStatus - oscillation width  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:16:240  - log-service  - updateColumnStatus called from: Trail Calculation - Completing  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:16:531  - log-service  - statusCrossCheck  - Updated, Rows affected : 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:16:924  - log-service  - updateColumnStatus called from: updateSLogsStatusFromTLogsStatus-JN_1  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:17:907  - log-service  - updateColumnStatus called from: leadStatus - travel speed  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:17:807  - log-service  - updateColumnStatus called from: leadStatus - wire speed  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:17:707  - log-service  - updateColumnStatus called from: leadStatus - current  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:17:401  - log-service  - updateColumnStatus called from: Lead Calculation - Starting  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:17:507  - log-service  - updateColumnStatus called from: Lead Calculation - Lead STATUS  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:17:607  - log-service  - updateColumnStatus called from: leadStatus - volts  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:18:741  - log-service  - updateColumnStatus called from: trailStatus - current  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:18:940  - log-service  - updateColumnStatus called from: trailStatus - travel speed  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:18:840  - log-service  - updateColumnStatus called from: trailStatus - wire speed  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:18:623  - log-service  - updateColumnStatus called from: trailStatus - volts  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:18:106  - log-service  - updateColumnStatus called from: Lead Calculation - Completing  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:18:454  - log-service  - updateColumnStatus called from: trail Calculation - Starting  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:18:007  - log-service  - updateColumnStatus called from: leadStatus - oscillation width  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:18:528  - log-service  - updateColumnStatus called from: trail Calculation - Trail STATUS  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:19:039  - log-service  - updateColumnStatus called from: trailStatus - oscillation width  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:19:139  - log-service  - updateColumnStatus called from: Trail Calculation - Completing  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:19:434  - log-service  - statusCrossCheck  - Updated, Rows affected : 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:19:823  - log-service  - updateColumnStatus called from: updateSLogsStatusFromTLogsStatus-JN_2  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:19:987  - log-service  - weldScreenErrorBanner  - Updated, Rows affected: 1</t>
+  </si>
+  <si>
+    <t>INFO : 15:44:21:781  - logService  - InsertsLogStatus - updating the status :   -</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:49:949  - CalculatingStatusModal  - startCalculating  - Start</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:53:904  - log-service  - checkTLogsExistenceByProjectId  - Rowcount: 248000</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:54:777  - log-service  - setIncompleteFlagTRecords  - Updated in s_logs, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:54:777  - log-service  - setIncompleteFlagTRecords  - Updated, Rows affected : 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:54:777  - log-service  - setIncompleteFlagTRecords  - Updated in clear, Rows affected: 248000</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:54:144  - CalculatingStatusModal  - startCalculating  - End</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:54:140  - CalculatingStatusModal  - startCalculating  - dbHelper-start</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:54:135  - CalculatingStatusModal  - startCalculating  - WeldParameters: true</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:54:132  - CalculatingStatusModal  - startCalculating  - tLogsPresent: true</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:55:913  - log-service  - updateLeadGroupNameTrailGroupName  - Updated, Rows affected : 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:56:836  - log-service  - updateColumnStatus called from: leadStatus - current  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:56:997  - log-service  - updateColumnStatus called from: leadStatus - wire speed  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:56:668  - log-service  - updateColumnStatus called from: leadStatus - volts  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:56:210  - log-service  - updateColumnStatus called from: Lead Calculation - Starting  - Updated, Rows affected: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:56:506  - log-service  - updateColumnStatus called from: Lead Calculation - Lead STATUS  - Updated, Rows affected: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:57:159  - log-service  - updateColumnStatus called from: leadStatus - travel speed  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:57:317  - log-service  - updateColumnStatus called from: leadStatus - oscillation width  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:57:610  - log-service  - updateColumnStatus called from: Lead Calculation - Completing  - Updated, Rows affected: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:57:909  - log-service  - updateColumnStatus called from: trail Calculation - Starting  - Updated, Rows affected: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:58:205  - log-service  - updateColumnStatus called from: trail Calculation - Trail STATUS  - Updated, Rows affected: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:58:367  - log-service  - updateColumnStatus called from: trailStatus - volts  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:58:529  - log-service  - updateColumnStatus called from: trailStatus - current  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:58:685  - log-service  - updateColumnStatus called from: trailStatus - wire speed  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:58:844  - log-service  - updateColumnStatus called from: trailStatus - travel speed  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:59:294  - log-service  - updateColumnStatus called from: Trail Calculation - Completing  - Updated, Rows affected: 124000</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:59:001  - log-service  - updateColumnStatus called from: trailStatus - oscillation width  - Updated, Rows affected: 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:52:59:349  - log-service  - statusCrossCheck  - Updated, Rows affected : 0</t>
+  </si>
+  <si>
+    <t>INFO : 15:53:03:826  - log-service  - trueAvgStatus  - Updated, Rows affected: 20000</t>
+  </si>
+  <si>
+    <t>3:35:30 PM</t>
+  </si>
+  <si>
+    <t>3:35:31 PM</t>
+  </si>
+  <si>
+    <t>0:00:01</t>
+  </si>
+  <si>
+    <t>3:35:32 PM</t>
+  </si>
+  <si>
+    <t>0:00:00</t>
+  </si>
+  <si>
+    <t>3:35:34 PM</t>
+  </si>
+  <si>
+    <t>3:35:35 PM</t>
+  </si>
+  <si>
+    <t>3:35:38 PM</t>
+  </si>
+  <si>
+    <t>3:35:41 PM</t>
+  </si>
+  <si>
+    <t>3:35:44 PM</t>
+  </si>
+  <si>
+    <t>3:35:48 PM</t>
+  </si>
+  <si>
+    <t>3:35:51 PM</t>
+  </si>
+  <si>
+    <t>3:35:52 PM</t>
+  </si>
+  <si>
+    <t>3:35:53 PM</t>
+  </si>
+  <si>
+    <t>3:35:54 PM</t>
+  </si>
+  <si>
+    <t>3:35:55 PM</t>
+  </si>
+  <si>
+    <t>3:35:56 PM</t>
+  </si>
+  <si>
+    <t>3:36:00 PM</t>
+  </si>
+  <si>
+    <t>3:39:18 PM</t>
+  </si>
+  <si>
+    <t>3:44:11 PM</t>
+  </si>
+  <si>
+    <t>3:44:12 PM</t>
+  </si>
+  <si>
+    <t>3:44:13 PM</t>
+  </si>
+  <si>
+    <t>3:44:14 PM</t>
+  </si>
+  <si>
+    <t>3:44:15 PM</t>
+  </si>
+  <si>
+    <t>3:44:16 PM</t>
+  </si>
+  <si>
+    <t>3:44:17 PM</t>
+  </si>
+  <si>
+    <t>3:44:18 PM</t>
+  </si>
+  <si>
+    <t>3:44:19 PM</t>
+  </si>
+  <si>
+    <t>3:44:21 PM</t>
+  </si>
+  <si>
+    <t>0:08:49</t>
+  </si>
+  <si>
+    <t>0:00:04</t>
+  </si>
+  <si>
+    <t>3:52:53 PM</t>
+  </si>
+  <si>
+    <t>3:52:54 PM</t>
+  </si>
+  <si>
+    <t>3:52:55 PM</t>
+  </si>
+  <si>
+    <t>3:52:56 PM</t>
+  </si>
+  <si>
+    <t>3:52:57 PM</t>
+  </si>
+  <si>
+    <t>3:52:58 PM</t>
+  </si>
+  <si>
+    <t>3:52:59 PM</t>
+  </si>
+  <si>
+    <t>0:00:09</t>
+  </si>
+  <si>
+    <t>3:53:03 PM</t>
   </si>
   <si>
     <t>0:00:02</t>
-  </si>
-  <si>
-    <t>0:00:09</t>
-  </si>
-  <si>
-    <t>0:01:11</t>
-  </si>
-  <si>
-    <t>0:00:01</t>
-  </si>
-  <si>
-    <t>0:01:07</t>
-  </si>
-  <si>
-    <t>0:00:11</t>
-  </si>
-  <si>
-    <t>0:00:51</t>
-  </si>
-  <si>
-    <t>0:00:07</t>
-  </si>
-  <si>
-    <t>0:01:08</t>
-  </si>
-  <si>
-    <t>0:04:42</t>
-  </si>
-  <si>
-    <t>0:00:46</t>
-  </si>
-  <si>
-    <t>Status calculation start</t>
-  </si>
-  <si>
-    <t>total tlogs in project</t>
-  </si>
-  <si>
-    <t>Total status calculation time</t>
-  </si>
-  <si>
-    <t>setIncomplete flag</t>
-  </si>
-  <si>
-    <t>status update</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:30:145  - CalculatingStatusModal  - startCalculating  - Start</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:31:995  - log-service  - checkTLogsExistenceByProjectId  - Rowcount: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:32:583  - log-service  - setIncompleteFlagTRecords  - Updated in s_logs, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:32:583  - log-service  - setIncompleteFlagTRecords  - Updated, Rows affected : 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:32:242  - CalculatingStatusModal  - startCalculating  - End</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:32:234  - CalculatingStatusModal  - startCalculating  - dbHelper-start</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:32:583  - log-service  - setIncompleteFlagTRecords  - Updated in clear, Rows affected: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:32:225  - CalculatingStatusModal  - startCalculating  - WeldParameters: true</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:32:211  - CalculatingStatusModal  - startCalculating  - tLogsPresent: true</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:34:101  - log-service  - updateLeadGroupNameTrailGroupName  - Updated, Rows affected : 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:34:577  - log-service  - updateColumnStatus called from: Lead Calculation - Starting  - Updated, Rows affected: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:35:062  - log-service  - updateColumnStatus called from: Lead Calculation - Lead STATUS  - Updated, Rows affected: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:38:380  - log-service  - updateColumnStatus called from: leadStatus - volts  - Updated, Rows affected: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:41:579  - log-service  - updateColumnStatus called from: leadStatus - current  - Updated, Rows affected: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:44:804  - log-service  - updateColumnStatus called from: leadStatus - wire speed  - Updated, Rows affected: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:48:078  - log-service  - updateColumnStatus called from: leadStatus - travel speed  - Updated, Rows affected: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:51:393  - log-service  - updateColumnStatus called from: leadStatus - oscillation width  - Updated, Rows affected: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:51:698  - log-service  - updateColumnStatus called from: Lead Calculation - Completing  - Updated, Rows affected: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:52:156  - log-service  - updateColumnStatus called from: trail Calculation - Starting  - Updated, Rows affected: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:52:614  - log-service  - updateColumnStatus called from: trail Calculation - Trail STATUS  - Updated, Rows affected: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:53:741  - log-service  - updateColumnStatus called from: trailStatus - volts  - Updated, Rows affected: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:54:614  - log-service  - updateColumnStatus called from: trailStatus - current  - Updated, Rows affected: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:55:693  - log-service  - updateColumnStatus called from: trailStatus - travel speed  - Updated, Rows affected: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:55:335  - log-service  - updateColumnStatus called from: trailStatus - wire speed  - Updated, Rows affected: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:56:078  - log-service  - updateColumnStatus called from: trailStatus - oscillation width  - Updated, Rows affected: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:56:371  - log-service  - updateColumnStatus called from: Trail Calculation - Completing  - Updated, Rows affected: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:35:56:564  - log-service  - statusCrossCheck  - Updated, Rows affected : 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:36:00:927  - log-service  - trueAvgStatus  - Updated, Rows affected: 20000</t>
-  </si>
-  <si>
-    <t>INFO : 15:39:18:233  - log-service  - trueTiltStatus  - Updated, Rows affected: 16000</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:11:045  - log-service  - updateColumnStatus called from: updateSLogsStatusFromTLogsStatus-Demo  - Updated, Rows affected: 4000</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:11:466  - log-service  - updateColumnStatus called from: Lead Calculation - Starting  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:11:598  - log-service  - updateColumnStatus called from: Lead Calculation - Lead STATUS  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:11:735  - log-service  - updateColumnStatus called from: leadStatus - volts  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:11:813  - log-service  - updateColumnStatus called from: leadStatus - current  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:11:918  - log-service  - updateColumnStatus called from: leadStatus - wire speed  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:12:701  - log-service  - updateColumnStatus called from: trail Calculation - Trail STATUS  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:12:992  - log-service  - updateColumnStatus called from: trailStatus - wire speed  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:12:892  - log-service  - updateColumnStatus called from: trailStatus - current  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:12:792  - log-service  - updateColumnStatus called from: trailStatus - volts  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:12:261  - log-service  - updateColumnStatus called from: Lead Calculation - Completing  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:12:145  - log-service  - updateColumnStatus called from: leadStatus - oscillation width  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:12:028  - log-service  - updateColumnStatus called from: leadStatus - travel speed  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:12:628  - log-service  - updateColumnStatus called from: trail Calculation - Starting  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:13:092  - log-service  - updateColumnStatus called from: trailStatus - travel speed  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:13:192  - log-service  - updateColumnStatus called from: trailStatus - oscillation width  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:13:309  - log-service  - updateColumnStatus called from: Trail Calculation - Completing  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:13:623  - log-service  - statusCrossCheck  - Updated, Rows affected : 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:14:809  - log-service  - updateColumnStatus called from: leadStatus - current  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:14:008  - log-service  - updateColumnStatus called from: updateSLogsStatusFromTLogsStatus-Demo_1  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:14:468  - log-service  - updateColumnStatus called from: Lead Calculation - Starting  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:14:575  - log-service  - updateColumnStatus called from: Lead Calculation - Lead STATUS  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:14:692  - log-service  - updateColumnStatus called from: leadStatus - volts  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:14:908  - log-service  - updateColumnStatus called from: leadStatus - wire speed  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:15:841  - log-service  - updateColumnStatus called from: trailStatus - current  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:15:941  - log-service  - updateColumnStatus called from: trailStatus - wire speed  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:15:631  - log-service  - updateColumnStatus called from: trail Calculation - Trail STATUS  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:15:742  - log-service  - updateColumnStatus called from: trailStatus - volts  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:15:207  - log-service  - updateColumnStatus called from: Lead Calculation - Completing  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:15:557  - log-service  - updateColumnStatus called from: trail Calculation - Starting  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:15:107  - log-service  - updateColumnStatus called from: leadStatus - oscillation width  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:15:008  - log-service  - updateColumnStatus called from: leadStatus - travel speed  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:16:041  - log-service  - updateColumnStatus called from: trailStatus - travel speed  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:16:140  - log-service  - updateColumnStatus called from: trailStatus - oscillation width  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:16:240  - log-service  - updateColumnStatus called from: Trail Calculation - Completing  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:16:531  - log-service  - statusCrossCheck  - Updated, Rows affected : 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:16:924  - log-service  - updateColumnStatus called from: updateSLogsStatusFromTLogsStatus-JN_1  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:17:907  - log-service  - updateColumnStatus called from: leadStatus - travel speed  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:17:807  - log-service  - updateColumnStatus called from: leadStatus - wire speed  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:17:707  - log-service  - updateColumnStatus called from: leadStatus - current  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:17:401  - log-service  - updateColumnStatus called from: Lead Calculation - Starting  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:17:507  - log-service  - updateColumnStatus called from: Lead Calculation - Lead STATUS  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:17:607  - log-service  - updateColumnStatus called from: leadStatus - volts  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:18:741  - log-service  - updateColumnStatus called from: trailStatus - current  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:18:940  - log-service  - updateColumnStatus called from: trailStatus - travel speed  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:18:840  - log-service  - updateColumnStatus called from: trailStatus - wire speed  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:18:623  - log-service  - updateColumnStatus called from: trailStatus - volts  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:18:106  - log-service  - updateColumnStatus called from: Lead Calculation - Completing  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:18:454  - log-service  - updateColumnStatus called from: trail Calculation - Starting  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:18:007  - log-service  - updateColumnStatus called from: leadStatus - oscillation width  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:18:528  - log-service  - updateColumnStatus called from: trail Calculation - Trail STATUS  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:19:039  - log-service  - updateColumnStatus called from: trailStatus - oscillation width  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:19:139  - log-service  - updateColumnStatus called from: Trail Calculation - Completing  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:19:434  - log-service  - statusCrossCheck  - Updated, Rows affected : 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:19:823  - log-service  - updateColumnStatus called from: updateSLogsStatusFromTLogsStatus-JN_2  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:19:987  - log-service  - weldScreenErrorBanner  - Updated, Rows affected: 1</t>
-  </si>
-  <si>
-    <t>INFO : 15:44:21:781  - logService  - InsertsLogStatus - updating the status :   -</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:49:949  - CalculatingStatusModal  - startCalculating  - Start</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:53:904  - log-service  - checkTLogsExistenceByProjectId  - Rowcount: 248000</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:54:777  - log-service  - setIncompleteFlagTRecords  - Updated in s_logs, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:54:777  - log-service  - setIncompleteFlagTRecords  - Updated, Rows affected : 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:54:777  - log-service  - setIncompleteFlagTRecords  - Updated in clear, Rows affected: 248000</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:54:144  - CalculatingStatusModal  - startCalculating  - End</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:54:140  - CalculatingStatusModal  - startCalculating  - dbHelper-start</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:54:135  - CalculatingStatusModal  - startCalculating  - WeldParameters: true</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:54:132  - CalculatingStatusModal  - startCalculating  - tLogsPresent: true</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:55:913  - log-service  - updateLeadGroupNameTrailGroupName  - Updated, Rows affected : 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:56:836  - log-service  - updateColumnStatus called from: leadStatus - current  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:56:997  - log-service  - updateColumnStatus called from: leadStatus - wire speed  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:56:668  - log-service  - updateColumnStatus called from: leadStatus - volts  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:56:210  - log-service  - updateColumnStatus called from: Lead Calculation - Starting  - Updated, Rows affected: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:56:506  - log-service  - updateColumnStatus called from: Lead Calculation - Lead STATUS  - Updated, Rows affected: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:57:159  - log-service  - updateColumnStatus called from: leadStatus - travel speed  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:57:317  - log-service  - updateColumnStatus called from: leadStatus - oscillation width  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:57:610  - log-service  - updateColumnStatus called from: Lead Calculation - Completing  - Updated, Rows affected: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:57:909  - log-service  - updateColumnStatus called from: trail Calculation - Starting  - Updated, Rows affected: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:58:205  - log-service  - updateColumnStatus called from: trail Calculation - Trail STATUS  - Updated, Rows affected: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:58:367  - log-service  - updateColumnStatus called from: trailStatus - volts  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:58:529  - log-service  - updateColumnStatus called from: trailStatus - current  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:58:685  - log-service  - updateColumnStatus called from: trailStatus - wire speed  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:58:844  - log-service  - updateColumnStatus called from: trailStatus - travel speed  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:59:294  - log-service  - updateColumnStatus called from: Trail Calculation - Completing  - Updated, Rows affected: 124000</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:59:001  - log-service  - updateColumnStatus called from: trailStatus - oscillation width  - Updated, Rows affected: 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:52:59:349  - log-service  - statusCrossCheck  - Updated, Rows affected : 0</t>
-  </si>
-  <si>
-    <t>INFO : 15:53:03:826  - log-service  - trueAvgStatus  - Updated, Rows affected: 20000</t>
-  </si>
-  <si>
-    <t>3:35:30 PM</t>
-  </si>
-  <si>
-    <t>3:35:31 PM</t>
-  </si>
-  <si>
-    <t>3:35:32 PM</t>
-  </si>
-  <si>
-    <t>0:00:00</t>
-  </si>
-  <si>
-    <t>3:35:34 PM</t>
-  </si>
-  <si>
-    <t>3:35:35 PM</t>
-  </si>
-  <si>
-    <t>3:35:38 PM</t>
-  </si>
-  <si>
-    <t>3:35:41 PM</t>
-  </si>
-  <si>
-    <t>3:35:44 PM</t>
-  </si>
-  <si>
-    <t>3:35:48 PM</t>
-  </si>
-  <si>
-    <t>3:35:51 PM</t>
-  </si>
-  <si>
-    <t>3:35:52 PM</t>
-  </si>
-  <si>
-    <t>3:35:53 PM</t>
-  </si>
-  <si>
-    <t>3:35:54 PM</t>
-  </si>
-  <si>
-    <t>3:35:55 PM</t>
-  </si>
-  <si>
-    <t>3:35:56 PM</t>
-  </si>
-  <si>
-    <t>3:36:00 PM</t>
-  </si>
-  <si>
-    <t>3:39:18 PM</t>
-  </si>
-  <si>
-    <t>3:44:11 PM</t>
-  </si>
-  <si>
-    <t>3:44:12 PM</t>
-  </si>
-  <si>
-    <t>3:44:13 PM</t>
-  </si>
-  <si>
-    <t>3:44:14 PM</t>
-  </si>
-  <si>
-    <t>3:44:15 PM</t>
-  </si>
-  <si>
-    <t>3:44:16 PM</t>
-  </si>
-  <si>
-    <t>3:44:17 PM</t>
-  </si>
-  <si>
-    <t>3:44:18 PM</t>
-  </si>
-  <si>
-    <t>3:44:19 PM</t>
-  </si>
-  <si>
-    <t>3:44:21 PM</t>
-  </si>
-  <si>
-    <t>0:08:49</t>
-  </si>
-  <si>
-    <t>0:00:04</t>
-  </si>
-  <si>
-    <t>3:52:53 PM</t>
-  </si>
-  <si>
-    <t>3:52:54 PM</t>
-  </si>
-  <si>
-    <t>3:52:55 PM</t>
-  </si>
-  <si>
-    <t>3:52:56 PM</t>
-  </si>
-  <si>
-    <t>3:52:57 PM</t>
-  </si>
-  <si>
-    <t>3:52:58 PM</t>
-  </si>
-  <si>
-    <t>3:52:59 PM</t>
-  </si>
-  <si>
-    <t>3:53:03 PM</t>
   </si>
   <si>
     <t>0:00:03</t>
@@ -1071,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
@@ -1079,9 +929,10 @@
     <col min="3" max="3" width="137.7109375" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1097,339 +948,102 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2">
+        <v>132000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>132000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="F7">
+        <v>132000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
         <v>18</v>
       </c>
-      <c r="D3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="E8" t="s">
         <v>19</v>
       </c>
-      <c r="D4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="B5" t="s">
+    </row>
+    <row r="9" spans="1:6">
+      <c r="B9" t="s">
         <v>8</v>
       </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="B6" t="s">
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10" t="s">
         <v>9</v>
       </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="B12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>2</v>
-      </c>
-      <c r="B16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5">
-      <c r="B17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5">
-      <c r="B18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5">
-      <c r="B19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5">
-      <c r="B20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20" t="s">
-        <v>55</v>
-      </c>
-      <c r="E20" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5">
-      <c r="B21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5">
-      <c r="B22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5">
-      <c r="B23" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5">
-      <c r="B24" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" t="s">
-        <v>57</v>
-      </c>
-      <c r="E24" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5">
-      <c r="B25" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" t="s">
-        <v>38</v>
-      </c>
-      <c r="D25" t="s">
-        <v>58</v>
-      </c>
-      <c r="E25" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5">
-      <c r="B26" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5">
-      <c r="B27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" t="s">
-        <v>39</v>
-      </c>
-      <c r="D27" t="s">
-        <v>60</v>
-      </c>
-      <c r="E27" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5">
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="s">
-        <v>40</v>
-      </c>
-      <c r="D28" t="s">
-        <v>60</v>
+      <c r="F10">
+        <v>264000</v>
       </c>
     </row>
   </sheetData>
@@ -1471,57 +1085,57 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>192</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="B3" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>193</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="B4" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>194</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>194</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1529,21 +1143,21 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>194</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>195</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1551,32 +1165,32 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>194</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="B12" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>194</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="B13" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>195</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1584,21 +1198,21 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>194</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="B17" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>195</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1606,940 +1220,940 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>194</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="B19" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>196</v>
+        <v>144</v>
       </c>
       <c r="E19" t="s">
-        <v>62</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="B20" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="D20" t="s">
-        <v>196</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="B21" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>197</v>
+        <v>145</v>
       </c>
       <c r="E21" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="B22" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>198</v>
+        <v>146</v>
       </c>
       <c r="E22" t="s">
-        <v>230</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="B23" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>91</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>199</v>
+        <v>147</v>
       </c>
       <c r="E23" t="s">
-        <v>230</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="B24" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>200</v>
+        <v>148</v>
       </c>
       <c r="E24" t="s">
-        <v>230</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="B25" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="D25" t="s">
-        <v>201</v>
+        <v>149</v>
       </c>
       <c r="E25" t="s">
-        <v>221</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="B26" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="D26" t="s">
-        <v>202</v>
+        <v>150</v>
       </c>
       <c r="E26" t="s">
-        <v>230</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="B27" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="D27" t="s">
-        <v>202</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="B28" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="D28" t="s">
-        <v>203</v>
+        <v>151</v>
       </c>
       <c r="E28" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="B29" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C29" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>203</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="B30" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C30" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="D30" t="s">
-        <v>204</v>
+        <v>152</v>
       </c>
       <c r="E30" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="B31" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C31" t="s">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="D31" t="s">
-        <v>205</v>
+        <v>153</v>
       </c>
       <c r="E31" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="B32" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="D32" t="s">
-        <v>206</v>
+        <v>154</v>
       </c>
     </row>
     <row r="33" spans="2:5">
       <c r="B33" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C33" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="D33" t="s">
-        <v>206</v>
+        <v>154</v>
       </c>
       <c r="E33" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
     </row>
     <row r="34" spans="2:5">
       <c r="B34" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="D34" t="s">
-        <v>207</v>
+        <v>155</v>
       </c>
       <c r="E34" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35" spans="2:5">
       <c r="B35" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C35" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="D35" t="s">
-        <v>207</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36" spans="2:5">
       <c r="B36" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C36" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="D36" t="s">
-        <v>207</v>
+        <v>155</v>
       </c>
     </row>
     <row r="37" spans="2:5">
       <c r="B37" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="D37" t="s">
-        <v>208</v>
+        <v>156</v>
       </c>
       <c r="E37" t="s">
-        <v>221</v>
+        <v>169</v>
       </c>
     </row>
     <row r="38" spans="2:5">
       <c r="B38" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="D38" t="s">
-        <v>209</v>
+        <v>157</v>
       </c>
       <c r="E38" t="s">
-        <v>231</v>
+        <v>181</v>
       </c>
     </row>
     <row r="39" spans="2:5">
       <c r="B39" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C39" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="D39" t="s">
-        <v>210</v>
+        <v>158</v>
       </c>
       <c r="E39" t="s">
-        <v>232</v>
+        <v>182</v>
       </c>
     </row>
     <row r="40" spans="2:5">
       <c r="B40" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C40" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="D40" t="s">
-        <v>210</v>
+        <v>158</v>
       </c>
     </row>
     <row r="41" spans="2:5">
       <c r="B41" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C41" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="D41" t="s">
-        <v>210</v>
+        <v>158</v>
       </c>
     </row>
     <row r="42" spans="2:5">
       <c r="B42" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C42" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="D42" t="s">
-        <v>210</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43" spans="2:5">
       <c r="B43" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C43" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="D43" t="s">
-        <v>210</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44" spans="2:5">
       <c r="B44" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C44" t="s">
-        <v>112</v>
+        <v>59</v>
       </c>
       <c r="D44" t="s">
-        <v>210</v>
+        <v>158</v>
       </c>
     </row>
     <row r="45" spans="2:5">
       <c r="B45" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C45" t="s">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="D45" t="s">
-        <v>211</v>
+        <v>159</v>
       </c>
     </row>
     <row r="46" spans="2:5">
       <c r="B46" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C46" t="s">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="D46" t="s">
-        <v>211</v>
+        <v>159</v>
       </c>
     </row>
     <row r="47" spans="2:5">
       <c r="B47" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C47" t="s">
-        <v>115</v>
+        <v>62</v>
       </c>
       <c r="D47" t="s">
-        <v>211</v>
+        <v>159</v>
       </c>
     </row>
     <row r="48" spans="2:5">
       <c r="B48" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C48" t="s">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="D48" t="s">
-        <v>211</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" spans="2:5">
       <c r="B49" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C49" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="D49" t="s">
-        <v>211</v>
+        <v>159</v>
       </c>
     </row>
     <row r="50" spans="2:5">
       <c r="B50" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C50" t="s">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="D50" t="s">
-        <v>211</v>
+        <v>159</v>
       </c>
     </row>
     <row r="51" spans="2:5">
       <c r="B51" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C51" t="s">
-        <v>119</v>
+        <v>66</v>
       </c>
       <c r="D51" t="s">
-        <v>211</v>
+        <v>159</v>
       </c>
       <c r="E51" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
     </row>
     <row r="52" spans="2:5">
       <c r="B52" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C52" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="D52" t="s">
-        <v>211</v>
+        <v>159</v>
       </c>
     </row>
     <row r="53" spans="2:5">
       <c r="B53" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C53" t="s">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="D53" t="s">
-        <v>212</v>
+        <v>160</v>
       </c>
       <c r="E53" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
     </row>
     <row r="54" spans="2:5">
       <c r="B54" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C54" t="s">
-        <v>122</v>
+        <v>69</v>
       </c>
       <c r="D54" t="s">
-        <v>212</v>
+        <v>160</v>
       </c>
     </row>
     <row r="55" spans="2:5">
       <c r="B55" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C55" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="D55" t="s">
-        <v>212</v>
+        <v>160</v>
       </c>
     </row>
     <row r="56" spans="2:5">
       <c r="B56" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C56" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="D56" t="s">
-        <v>212</v>
+        <v>160</v>
       </c>
     </row>
     <row r="57" spans="2:5">
       <c r="B57" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C57" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="D57" t="s">
-        <v>213</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58" spans="2:5">
       <c r="B58" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C58" t="s">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="D58" t="s">
-        <v>213</v>
+        <v>161</v>
       </c>
       <c r="E58" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59" spans="2:5">
       <c r="B59" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C59" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="D59" t="s">
-        <v>213</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" spans="2:5">
       <c r="B60" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C60" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="D60" t="s">
-        <v>213</v>
+        <v>161</v>
       </c>
     </row>
     <row r="61" spans="2:5">
       <c r="B61" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C61" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="D61" t="s">
-        <v>213</v>
+        <v>161</v>
       </c>
     </row>
     <row r="62" spans="2:5">
       <c r="B62" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" t="s">
         <v>77</v>
       </c>
-      <c r="C62" t="s">
-        <v>130</v>
-      </c>
       <c r="D62" t="s">
-        <v>213</v>
+        <v>161</v>
       </c>
     </row>
     <row r="63" spans="2:5">
       <c r="B63" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C63" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="D63" t="s">
-        <v>214</v>
+        <v>162</v>
       </c>
     </row>
     <row r="64" spans="2:5">
       <c r="B64" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C64" t="s">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="D64" t="s">
-        <v>214</v>
+        <v>162</v>
       </c>
     </row>
     <row r="65" spans="2:5">
       <c r="B65" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C65" t="s">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="D65" t="s">
-        <v>214</v>
+        <v>162</v>
       </c>
     </row>
     <row r="66" spans="2:5">
       <c r="B66" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C66" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="D66" t="s">
-        <v>214</v>
+        <v>162</v>
       </c>
     </row>
     <row r="67" spans="2:5">
       <c r="B67" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C67" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="D67" t="s">
-        <v>214</v>
+        <v>162</v>
       </c>
     </row>
     <row r="68" spans="2:5">
       <c r="B68" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C68" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="D68" t="s">
-        <v>214</v>
+        <v>162</v>
       </c>
     </row>
     <row r="69" spans="2:5">
       <c r="B69" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C69" t="s">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="D69" t="s">
-        <v>214</v>
+        <v>162</v>
       </c>
     </row>
     <row r="70" spans="2:5">
       <c r="B70" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C70" t="s">
-        <v>138</v>
+        <v>85</v>
       </c>
       <c r="D70" t="s">
-        <v>214</v>
+        <v>162</v>
       </c>
       <c r="E70" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
     </row>
     <row r="71" spans="2:5">
       <c r="B71" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C71" t="s">
-        <v>139</v>
+        <v>86</v>
       </c>
       <c r="D71" t="s">
-        <v>215</v>
+        <v>163</v>
       </c>
       <c r="E71" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
     </row>
     <row r="72" spans="2:5">
       <c r="B72" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C72" t="s">
-        <v>140</v>
+        <v>87</v>
       </c>
       <c r="D72" t="s">
-        <v>215</v>
+        <v>163</v>
       </c>
     </row>
     <row r="73" spans="2:5">
       <c r="B73" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C73" t="s">
-        <v>141</v>
+        <v>88</v>
       </c>
       <c r="D73" t="s">
-        <v>215</v>
+        <v>163</v>
       </c>
     </row>
     <row r="74" spans="2:5">
       <c r="B74" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C74" t="s">
-        <v>142</v>
+        <v>89</v>
       </c>
       <c r="D74" t="s">
-        <v>215</v>
+        <v>163</v>
       </c>
     </row>
     <row r="75" spans="2:5">
       <c r="B75" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C75" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="D75" t="s">
-        <v>215</v>
+        <v>163</v>
       </c>
     </row>
     <row r="76" spans="2:5">
       <c r="B76" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C76" t="s">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="D76" t="s">
-        <v>216</v>
+        <v>164</v>
       </c>
     </row>
     <row r="77" spans="2:5">
       <c r="B77" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C77" t="s">
-        <v>145</v>
+        <v>92</v>
       </c>
       <c r="D77" t="s">
-        <v>216</v>
+        <v>164</v>
       </c>
     </row>
     <row r="78" spans="2:5">
       <c r="B78" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C78" t="s">
-        <v>146</v>
+        <v>93</v>
       </c>
       <c r="D78" t="s">
-        <v>216</v>
+        <v>164</v>
       </c>
     </row>
     <row r="79" spans="2:5">
       <c r="B79" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C79" t="s">
-        <v>147</v>
+        <v>94</v>
       </c>
       <c r="D79" t="s">
-        <v>216</v>
+        <v>164</v>
       </c>
       <c r="E79" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
     </row>
     <row r="80" spans="2:5">
       <c r="B80" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C80" t="s">
-        <v>148</v>
+        <v>95</v>
       </c>
       <c r="D80" t="s">
-        <v>216</v>
+        <v>164</v>
       </c>
     </row>
     <row r="81" spans="2:5">
       <c r="B81" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C81" t="s">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c r="D81" t="s">
-        <v>216</v>
+        <v>164</v>
       </c>
     </row>
     <row r="82" spans="2:5">
       <c r="B82" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C82" t="s">
-        <v>150</v>
+        <v>97</v>
       </c>
       <c r="D82" t="s">
-        <v>217</v>
+        <v>165</v>
       </c>
     </row>
     <row r="83" spans="2:5">
       <c r="B83" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C83" t="s">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="D83" t="s">
-        <v>217</v>
+        <v>165</v>
       </c>
     </row>
     <row r="84" spans="2:5">
       <c r="B84" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C84" t="s">
-        <v>152</v>
+        <v>99</v>
       </c>
       <c r="D84" t="s">
-        <v>217</v>
+        <v>165</v>
       </c>
     </row>
     <row r="85" spans="2:5">
       <c r="B85" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C85" t="s">
-        <v>153</v>
+        <v>100</v>
       </c>
       <c r="D85" t="s">
-        <v>217</v>
+        <v>165</v>
       </c>
     </row>
     <row r="86" spans="2:5">
       <c r="B86" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C86" t="s">
-        <v>154</v>
+        <v>101</v>
       </c>
       <c r="D86" t="s">
-        <v>217</v>
+        <v>165</v>
       </c>
     </row>
     <row r="87" spans="2:5">
       <c r="B87" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C87" t="s">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="D87" t="s">
-        <v>217</v>
+        <v>165</v>
       </c>
     </row>
     <row r="88" spans="2:5">
       <c r="B88" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C88" t="s">
-        <v>156</v>
+        <v>103</v>
       </c>
       <c r="D88" t="s">
-        <v>217</v>
+        <v>165</v>
       </c>
       <c r="E88" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
     </row>
     <row r="89" spans="2:5">
       <c r="B89" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C89" t="s">
-        <v>157</v>
+        <v>104</v>
       </c>
       <c r="D89" t="s">
-        <v>217</v>
+        <v>165</v>
       </c>
     </row>
     <row r="90" spans="2:5">
       <c r="B90" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C90" t="s">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="D90" t="s">
-        <v>218</v>
+        <v>166</v>
       </c>
       <c r="E90" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
     </row>
     <row r="91" spans="2:5">
       <c r="B91" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C91" t="s">
-        <v>159</v>
+        <v>106</v>
       </c>
       <c r="D91" t="s">
-        <v>218</v>
+        <v>166</v>
       </c>
     </row>
     <row r="92" spans="2:5">
       <c r="B92" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C92" t="s">
-        <v>160</v>
+        <v>107</v>
       </c>
       <c r="D92" t="s">
-        <v>218</v>
+        <v>166</v>
       </c>
     </row>
     <row r="93" spans="2:5">
       <c r="B93" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C93" t="s">
-        <v>161</v>
+        <v>108</v>
       </c>
       <c r="D93" t="s">
-        <v>218</v>
+        <v>166</v>
       </c>
     </row>
     <row r="94" spans="2:5">
       <c r="B94" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C94" t="s">
-        <v>162</v>
+        <v>109</v>
       </c>
       <c r="D94" t="s">
-        <v>218</v>
+        <v>166</v>
       </c>
     </row>
     <row r="95" spans="2:5">
       <c r="B95" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C95" t="s">
-        <v>163</v>
+        <v>110</v>
       </c>
       <c r="D95" t="s">
-        <v>219</v>
+        <v>167</v>
       </c>
       <c r="E95" t="s">
-        <v>62</v>
+        <v>179</v>
       </c>
     </row>
     <row r="96" spans="2:5">
       <c r="B96" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="D96" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2547,68 +2161,68 @@
         <v>6</v>
       </c>
       <c r="B98" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="C98" t="s">
-        <v>164</v>
+        <v>111</v>
       </c>
       <c r="D98" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="B99" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="D99" t="s">
-        <v>221</v>
+        <v>169</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="B101" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="C101" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="D101" t="s">
-        <v>222</v>
+        <v>170</v>
       </c>
       <c r="E101" t="s">
-        <v>221</v>
+        <v>169</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="B102" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="C102" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="D102" t="s">
-        <v>223</v>
+        <v>171</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="B103" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="C103" t="s">
-        <v>167</v>
+        <v>114</v>
       </c>
       <c r="D103" t="s">
-        <v>223</v>
+        <v>171</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="B104" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="C104" t="s">
-        <v>168</v>
+        <v>115</v>
       </c>
       <c r="D104" t="s">
-        <v>223</v>
+        <v>171</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2616,13 +2230,13 @@
         <v>10</v>
       </c>
       <c r="B105" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="C105" t="s">
-        <v>169</v>
+        <v>116</v>
       </c>
       <c r="D105" t="s">
-        <v>223</v>
+        <v>171</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2630,29 +2244,29 @@
         <v>9</v>
       </c>
       <c r="B107" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="C107" t="s">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="D107" t="s">
-        <v>223</v>
+        <v>171</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="B108" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="D108" t="s">
-        <v>195</v>
+        <v>143</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="B109" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="D109" t="s">
-        <v>195</v>
+        <v>143</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2660,21 +2274,21 @@
         <v>8</v>
       </c>
       <c r="B110" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="C110" t="s">
+        <v>118</v>
+      </c>
+      <c r="D110" t="s">
         <v>171</v>
-      </c>
-      <c r="D110" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="B112" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="D112" t="s">
-        <v>195</v>
+        <v>143</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2682,248 +2296,248 @@
         <v>7</v>
       </c>
       <c r="B113" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="C113" t="s">
-        <v>172</v>
+        <v>119</v>
       </c>
       <c r="D113" t="s">
-        <v>223</v>
+        <v>171</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="B115" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C115" t="s">
-        <v>173</v>
+        <v>120</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>172</v>
       </c>
       <c r="E115" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="B116" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C116" t="s">
-        <v>174</v>
+        <v>121</v>
       </c>
       <c r="D116" t="s">
-        <v>225</v>
+        <v>173</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="B117" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C117" t="s">
-        <v>175</v>
+        <v>122</v>
       </c>
       <c r="D117" t="s">
-        <v>225</v>
+        <v>173</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="B118" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C118" t="s">
-        <v>176</v>
+        <v>123</v>
       </c>
       <c r="D118" t="s">
-        <v>225</v>
+        <v>173</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="B119" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C119" t="s">
-        <v>177</v>
+        <v>124</v>
       </c>
       <c r="D119" t="s">
-        <v>225</v>
+        <v>173</v>
       </c>
       <c r="E119" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="B120" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C120" t="s">
-        <v>178</v>
+        <v>125</v>
       </c>
       <c r="D120" t="s">
-        <v>225</v>
+        <v>173</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="B121" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C121" t="s">
-        <v>179</v>
+        <v>126</v>
       </c>
       <c r="D121" t="s">
-        <v>226</v>
+        <v>174</v>
       </c>
       <c r="E121" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="B122" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C122" t="s">
-        <v>180</v>
+        <v>127</v>
       </c>
       <c r="D122" t="s">
-        <v>226</v>
+        <v>174</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="B123" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C123" t="s">
-        <v>181</v>
+        <v>128</v>
       </c>
       <c r="D123" t="s">
-        <v>226</v>
+        <v>174</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="B124" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C124" t="s">
-        <v>182</v>
+        <v>129</v>
       </c>
       <c r="D124" t="s">
-        <v>226</v>
+        <v>174</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="B125" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C125" t="s">
-        <v>183</v>
+        <v>130</v>
       </c>
       <c r="D125" t="s">
-        <v>227</v>
+        <v>175</v>
       </c>
       <c r="E125" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="B126" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C126" t="s">
-        <v>184</v>
+        <v>131</v>
       </c>
       <c r="D126" t="s">
-        <v>227</v>
+        <v>175</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="B127" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C127" t="s">
-        <v>185</v>
+        <v>132</v>
       </c>
       <c r="D127" t="s">
-        <v>227</v>
+        <v>175</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="B128" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C128" t="s">
-        <v>186</v>
+        <v>133</v>
       </c>
       <c r="D128" t="s">
-        <v>227</v>
+        <v>175</v>
       </c>
     </row>
     <row r="129" spans="2:5">
       <c r="B129" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C129" t="s">
-        <v>187</v>
+        <v>134</v>
       </c>
       <c r="D129" t="s">
-        <v>227</v>
+        <v>175</v>
       </c>
     </row>
     <row r="130" spans="2:5">
       <c r="B130" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C130" t="s">
-        <v>188</v>
+        <v>135</v>
       </c>
       <c r="D130" t="s">
-        <v>228</v>
+        <v>176</v>
       </c>
     </row>
     <row r="131" spans="2:5">
       <c r="B131" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C131" t="s">
-        <v>189</v>
+        <v>136</v>
       </c>
       <c r="D131" t="s">
-        <v>228</v>
+        <v>176</v>
       </c>
       <c r="E131" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
     </row>
     <row r="132" spans="2:5">
       <c r="B132" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C132" t="s">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="D132" t="s">
-        <v>228</v>
+        <v>176</v>
       </c>
     </row>
     <row r="133" spans="2:5">
       <c r="B133" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="D133" t="s">
-        <v>63</v>
+        <v>177</v>
       </c>
     </row>
     <row r="134" spans="2:5">
       <c r="B134" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C134" t="s">
-        <v>191</v>
+        <v>138</v>
       </c>
       <c r="D134" t="s">
-        <v>229</v>
+        <v>178</v>
       </c>
       <c r="E134" t="s">
-        <v>221</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
